--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -2807,7 +2807,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -2985,7 +2985,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>1, 2 or 3, from your Platform Control Levels.</t>
+          <t>Level 1 Hand-scoped, Level 2 Classification ceiling, Level 3 Policy as code. Defined in your Platform Control Levels.</t>
         </is>
       </c>
       <c r="B17" s="32" t="n"/>
@@ -3814,7 +3814,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C16 C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Level 1,Level 2,Level 3"</formula1>
+      <formula1>"Level 1 — Hand-scoped,Level 2 — Classification ceiling,Level 3 — Policy as code"</formula1>
     </dataValidation>
     <dataValidation sqref="F78:F87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
@@ -3844,7 +3844,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -3950,7 +3950,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Monitoring level of the platform it runs on: 1, 2 or 3</t>
+          <t>Monitoring level of the platform it runs on: Level 1 Tool call log, Level 2 Run records, Level 3 Replay and test</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -5089,7 +5089,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C10 C11 C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Level 1,Level 2,Level 3"</formula1>
+      <formula1>"Level 1 — Tool call log,Level 2 — Run records,Level 3 — Replay and test"</formula1>
     </dataValidation>
     <dataValidation sqref="B18:B25 E47:E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,Partly"</formula1>
@@ -6319,7 +6319,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="86" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -6560,7 +6560,7 @@
       <c r="A24" s="32" t="n"/>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 1 — Hand-scoped</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -6573,7 +6573,7 @@
       <c r="A25" s="32" t="n"/>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 — Classification ceiling</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -6586,7 +6586,7 @@
       <c r="A26" s="32" t="n"/>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 3 — Policy as code</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -6619,7 +6619,7 @@
       <c r="A29" s="32" t="n"/>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 1 — Tool call log</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -6632,7 +6632,7 @@
       <c r="A30" s="32" t="n"/>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 — Run records</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -6645,7 +6645,7 @@
       <c r="A31" s="32" t="n"/>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 3 — Replay and test</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Agent Design" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Classification" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2a Floor Anchors" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Platform &amp; Sign-off" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Monitoring" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Audit &amp; Assurance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1 Agent Design" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2 Classification" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2a Floor Anchors" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3 Platform &amp; Sign-off" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4 Monitoring" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5 Audit &amp; Assurance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6 Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Agent Design'!$1:$2</definedName>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -336,6 +336,10 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -410,39 +414,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1714500" cy="771525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -972,7 +943,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2171,7 +2141,7 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Which regulations reach this process? Name them, or write "none that we have identified" and say who looked.</t>
+          <t>Which regulations reach this process? Name them, or write "none that we have identified". Either way, name the legal, compliance or privacy adviser who determined it.</t>
         </is>
       </c>
       <c r="C13" s="35" t="n"/>
@@ -2249,8 +2219,12 @@
       <c r="E18" s="35" t="n"/>
       <c r="F18" s="34" t="n"/>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="32" t="n"/>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Question 3 is not a question this form answers, and not one the agent’s team answers on its own. Which regulations reach a process is a determination from whoever advises your company on regulation — legal, compliance, or privacy. Record their answer in the row and name them; "none that we have identified" with nobody named behind it leaves the row unanswered.</t>
+        </is>
+      </c>
       <c r="B19" s="32" t="n"/>
       <c r="C19" s="32" t="n"/>
       <c r="D19" s="32" t="n"/>
@@ -2385,7 +2359,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A27:F27"/>
@@ -2407,6 +2381,7 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A32:B32"/>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 Agent Design" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2 Classification" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2a Floor Anchors" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3 Platform &amp; Sign-off" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4 Monitoring" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5 Audit &amp; Assurance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="6 Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Agent Design" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Classification" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2a Floor Anchors" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Platform &amp; Sign-off" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Monitoring" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Audit &amp; Assurance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Agent Design'!$1:$2</definedName>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -336,10 +336,6 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,6 +410,39 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="771525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -943,6 +972,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2219,8 +2249,8 @@
       <c r="E18" s="35" t="n"/>
       <c r="F18" s="34" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="39" t="inlineStr">
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Question 3 is not a question this form answers, and not one the agent’s team answers on its own. Which regulations reach a process is a determination from whoever advises your company on regulation — legal, compliance, or privacy. Record their answer in the row and name them; "none that we have identified" with nobody named behind it leaves the row unanswered.</t>
         </is>
@@ -2360,6 +2390,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="32">
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A27:F27"/>
@@ -2381,7 +2412,6 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A32:B32"/>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -1494,10 +1494,10 @@
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="34" t="n"/>
     </row>
-    <row r="49" ht="13" customHeight="1">
+    <row r="49" ht="70" customHeight="70">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>The most money or value the agent can move in one action, and in one day. Write "none" if there is no ceiling, and expect the Classification sheet to charge you for it.</t>
+          <t>The most money or value the agent can move in one action, and in one day, stated for each kind of movement it can make: money out (payments, refunds, credits, discounts), money in (charges, invoices, collections), and commitments that become money later (orders, contracts, billable provisioning). Value that is not currency counts: inventory, store credit, points, gift cards, licences. Write "none" against a kind that has no ceiling, and expect the Classification sheet to charge you for it.</t>
         </is>
       </c>
     </row>
@@ -2179,13 +2179,13 @@
       <c r="E13" s="35" t="n"/>
       <c r="F13" s="34" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="48" customHeight="48">
       <c r="A14" s="17" t="n">
         <v>4</v>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>How much money or value can it move, in one action and in one day?</t>
+          <t>How much money or value can it move, in one action and in one day? Answer for each kind of movement it can make: money out, money in, and commitments that become money later.</t>
         </is>
       </c>
       <c r="C14" s="35" t="n"/>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>It moves no money or value.</t>
+          <t>It moves no money or value: none out, none in, and it commits none.</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>It moves money or value within a ceiling that covers both one action and one day, recorded in its design document.</t>
+          <t>Every kind of movement it makes is within a ceiling that covers both one action and one day, recorded in its design document.</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>The ceiling covers one action but not one day, or nothing approves the actions that reach it.</t>
+          <t>A ceiling covers one action but not one day, or nothing approves the actions that reach it.</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>No ceiling, or a ceiling the agent observes itself rather than one the platform enforces.</t>
+          <t>A kind of movement it can make has no ceiling, or has one the agent observes itself rather than one the platform enforces.</t>
         </is>
       </c>
     </row>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="44" customHeight="1">
+    <row r="17" ht="100" customHeight="100">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Question 4 sets no amount, and this pack names none. What a given agent may move is the value ceiling in section 3 of its Agent Design sheet, accepted by whoever signs it off. The anchors judge the shape of the control instead: whether a ceiling exists, whether it covers a day as well as an action, and whether the platform enforces it or the agent is trusted to observe it. Question 7 is the one row where the anchors describe supervision instead of damage: it is what turns the other seven into risk.</t>
+          <t>Question 4 covers three kinds of movement, and most agents that reach it do more than one: money out (paying, refunding, crediting, discounting), money in (charging, invoicing, collecting) and commitments that become money later (orders, contracts, billable provisioning). Value that is not currency counts on the same footing: inventory, store credit, points, gift cards, licences. Answer for every kind the agent can do, name a ceiling for each, and take the highest floor any of them sets. Question 4 sets no amount, and this pack names none. What a given agent may move is the value ceiling in section 3 of its Agent Design sheet, accepted by whoever signs it off. The anchors judge the shape of the control instead: whether a ceiling exists, whether it covers a day as well as an action, and whether the platform enforces it or the agent is trusted to observe it. Question 7 is the one row where the anchors describe supervision instead of damage: it is what turns the other seven into risk.</t>
         </is>
       </c>
     </row>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -2966,7 +2966,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>How the credentials are revoked, by whom, and how long that takes</t>
+          <t>How the credentials are revoked, by whom, and how long that takes, measured to the point the existing credentials stop working</t>
         </is>
       </c>
       <c r="B15" s="15" t="n"/>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Can you undo what it does? Name the action that is hardest to undo, and how long you have.</t>
+          <t>Can you undo what it does? Name the action that is hardest to undo, and how long you have from the moment it takes effect.</t>
         </is>
       </c>
       <c r="C15" s="35" t="n"/>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Reversible by the team within one working day.</t>
+          <t>Reversible by the team within one working day of the action taking effect.</t>
         </is>
       </c>
       <c r="E12" s="35" t="inlineStr">
         <is>
-          <t>Reversible only with another party's help, or beyond one working day.</t>
+          <t>Reversible only with another party's help, or beyond one working day of the action taking effect.</t>
         </is>
       </c>
       <c r="F12" s="35" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="40" ht="56" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>How you would know they had stopped running</t>
+          <t>How you would know they had stopped running, and how long after the run that did not happen</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
@@ -5641,7 +5641,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>How you would know the evals had stopped running</t>
+          <t>How you would know the evals had stopped running, and how long after the run that did not happen</t>
         </is>
       </c>
       <c r="B49" s="15" t="n"/>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -2807,7 +2807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3158,7 +3158,11 @@
           <t>Wider, narrower, or the same</t>
         </is>
       </c>
-      <c r="E33" s="16" t="n"/>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Where it is enforced</t>
+        </is>
+      </c>
       <c r="F33" s="15" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
@@ -3166,7 +3170,7 @@
       <c r="B34" s="35" t="n"/>
       <c r="C34" s="34" t="n"/>
       <c r="D34" s="35" t="n"/>
-      <c r="E34" s="36" t="n"/>
+      <c r="E34" s="35" t="n"/>
       <c r="F34" s="34" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
@@ -3174,7 +3178,7 @@
       <c r="B35" s="35" t="n"/>
       <c r="C35" s="34" t="n"/>
       <c r="D35" s="35" t="n"/>
-      <c r="E35" s="36" t="n"/>
+      <c r="E35" s="35" t="n"/>
       <c r="F35" s="34" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
@@ -3182,117 +3186,100 @@
       <c r="B36" s="35" t="n"/>
       <c r="C36" s="34" t="n"/>
       <c r="D36" s="35" t="n"/>
-      <c r="E36" s="36" t="n"/>
+      <c r="E36" s="35" t="n"/>
       <c r="F36" s="34" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="32" t="n"/>
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="32" t="n"/>
-      <c r="D37" s="32" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-    </row>
-    <row r="38" ht="56" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A37" s="35" t="n"/>
+      <c r="B37" s="35" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="35" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="34" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="35" t="n"/>
+      <c r="B38" s="35" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="34" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="35" t="n"/>
+      <c r="B39" s="35" t="n"/>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="34" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="35" t="n"/>
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="34" t="n"/>
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="34" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="35" t="n"/>
+      <c r="B41" s="35" t="n"/>
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="35" t="n"/>
+      <c r="E41" s="35" t="n"/>
+      <c r="F41" s="34" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="35" t="n"/>
+      <c r="B42" s="35" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="D42" s="35" t="n"/>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="34" t="n"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="35" t="n"/>
+      <c r="B43" s="35" t="n"/>
+      <c r="C43" s="34" t="n"/>
+      <c r="D43" s="35" t="n"/>
+      <c r="E43" s="35" t="n"/>
+      <c r="F43" s="34" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="35" t="n"/>
+      <c r="B44" s="35" t="n"/>
+      <c r="C44" s="34" t="n"/>
+      <c r="D44" s="35" t="n"/>
+      <c r="E44" s="35" t="n"/>
+      <c r="F44" s="34" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="35" t="n"/>
+      <c r="B45" s="35" t="n"/>
+      <c r="C45" s="34" t="n"/>
+      <c r="D45" s="35" t="n"/>
+      <c r="E45" s="35" t="n"/>
+      <c r="F45" s="34" t="n"/>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>Add rows until every row of section 3 has one here — select a row inside the table and insert, then copy an existing row down so the dropdowns come with it. A summary of thirty grants is not this table. "Nowhere" in the last column is an honest answer: the row is a sentence in a document rather than a control, and it belongs in section C as remaining risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="32" t="n"/>
+      <c r="B47" s="32" t="n"/>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+    </row>
+    <row r="48" ht="56" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Anything narrower than the design document asks for</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="35" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="34" t="n"/>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>Say what the agent cannot do as a result, and whether anybody has worked around it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="56" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>What is granted that the design document does not list</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="36" t="n"/>
-      <c r="E40" s="36" t="n"/>
-      <c r="F40" s="34" t="n"/>
-    </row>
-    <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Anything the agent can reach that section 3 does not name. This should be empty. Where it is not, carry it into section C as remaining risk. Do not fix it quietly and leave this blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="32" t="n"/>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="D42" s="32" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>B.  What the evals found   (against the setup in section A, not a development configuration)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Which evals you ran</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="35" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
-      <c r="F44" s="34" t="n"/>
-    </row>
-    <row r="45" ht="56" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Adversarial testing performed, and what it was tested against</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="n"/>
-      <c r="C45" s="35" t="n"/>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
-      <c r="F45" s="34" t="n"/>
-    </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>For any agent that reads content it did not author, whether it can be talked into something is what the sign-off most needs to know. Name what you tested against from OWASP's Top 10 for Agentic Applications, the same list the Monitoring sheet's playbook works from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Against which configuration, matching section A</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="35" t="n"/>
-      <c r="D47" s="36" t="n"/>
-      <c r="E47" s="36" t="n"/>
-      <c r="F47" s="34" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
         </is>
       </c>
       <c r="B48" s="15" t="n"/>
@@ -3301,41 +3288,36 @@
       <c r="E48" s="36" t="n"/>
       <c r="F48" s="34" t="n"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>What they found</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="35" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="34" t="n"/>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>This is what the person signing off is accepting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>What you changed because of it</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="35" t="n"/>
-      <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="n"/>
-      <c r="F51" s="34" t="n"/>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>Say what the agent cannot do as a result, and whether anybody has worked around it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="56" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>What is granted that the design document does not list</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="35" t="n"/>
+      <c r="D50" s="36" t="n"/>
+      <c r="E50" s="36" t="n"/>
+      <c r="F50" s="34" t="n"/>
+    </row>
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>Anything the agent can reach that section 3 does not name. This should be empty. Where it is not, carry it into section C as remaining risk. Do not fix it quietly and leave this blank.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="56" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>What you know you did NOT test</t>
+          <t>Limits the platform cannot express</t>
         </is>
       </c>
       <c r="B52" s="15" t="n"/>
@@ -3344,44 +3326,44 @@
       <c r="E52" s="36" t="n"/>
       <c r="F52" s="34" t="n"/>
     </row>
-    <row r="53" ht="13" customHeight="1">
+    <row r="53" ht="40" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>This is where stage 4 monitoring has to begin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Where the results are kept</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="35" t="n"/>
-      <c r="D54" s="36" t="n"/>
-      <c r="E54" s="36" t="n"/>
-      <c r="F54" s="34" t="n"/>
-    </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="32" t="n"/>
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="32" t="n"/>
-      <c r="D55" s="32" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>C.  Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t>Every row of section 3 whose granularity is "not enforceable here": a boundary declared in stage 1 that nothing here can hold. Say what the agent can reach as a result, and carry these into section C as remaining risk. The row above is access nobody meant to grant; this one is a limit nobody can enforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="32" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>B.  What the evals found   (against the setup in section A, not a development configuration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Which evals you ran</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="35" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="34" t="n"/>
+    </row>
+    <row r="57" ht="56" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Adversarial testing performed, and what it was tested against</t>
         </is>
       </c>
       <c r="B57" s="15" t="n"/>
@@ -3390,22 +3372,17 @@
       <c r="E57" s="36" t="n"/>
       <c r="F57" s="34" t="n"/>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="n"/>
-      <c r="C58" s="35" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="34" t="n"/>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>For any agent that reads content it did not author, whether it can be talked into something is what the sign-off most needs to know. Name what you tested against from OWASP's Top 10 for Agentic Applications, the same list the Monitoring sheet's playbook works from.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Against which configuration, matching section A</t>
         </is>
       </c>
       <c r="B59" s="15" t="n"/>
@@ -3417,7 +3394,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Version of the design document signed</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="B60" s="15" t="n"/>
@@ -3426,10 +3403,10 @@
       <c r="E60" s="36" t="n"/>
       <c r="F60" s="34" t="n"/>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="61" ht="56" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Version of this record signed</t>
+          <t>What they found</t>
         </is>
       </c>
       <c r="B61" s="15" t="n"/>
@@ -3438,22 +3415,17 @@
       <c r="E61" s="36" t="n"/>
       <c r="F61" s="34" t="n"/>
     </row>
-    <row r="62" ht="56" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>The risk that is left, stated in their words</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="35" t="n"/>
-      <c r="D62" s="36" t="n"/>
-      <c r="E62" s="36" t="n"/>
-      <c r="F62" s="34" t="n"/>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>This is what the person signing off is accepting.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Any classification floor lowered by a compensating control</t>
+          <t>What you changed because of it</t>
         </is>
       </c>
       <c r="B63" s="15" t="n"/>
@@ -3462,60 +3434,56 @@
       <c r="E63" s="36" t="n"/>
       <c r="F63" s="34" t="n"/>
     </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>A floor lowered in the design document and not repeated here has not been accepted by anybody.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="56" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Conditions on the sign-off, and when it must be looked at again</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="n"/>
-      <c r="C65" s="35" t="n"/>
-      <c r="D65" s="36" t="n"/>
-      <c r="E65" s="36" t="n"/>
-      <c r="F65" s="34" t="n"/>
+    <row r="64" ht="56" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>What you know you did NOT test</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="35" t="n"/>
+      <c r="D64" s="36" t="n"/>
+      <c r="E64" s="36" t="n"/>
+      <c r="F64" s="34" t="n"/>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>This is where stage 4 monitoring has to begin.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="24" t="inlineStr">
-        <is>
-          <t>THE LEVEL GAP.  The agent's classification names a platform control level and a monitoring level that an agent in it requires. Where the level applied is lower, the gap is accepted here, by name, or it is not accepted at all.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Platform control level the classification requires, and the level applied</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="n"/>
-      <c r="C67" s="35" t="n"/>
-      <c r="D67" s="36" t="n"/>
-      <c r="E67" s="36" t="n"/>
-      <c r="F67" s="34" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Monitoring level the classification requires, and the level applied</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="n"/>
-      <c r="C68" s="35" t="n"/>
-      <c r="D68" s="36" t="n"/>
-      <c r="E68" s="36" t="n"/>
-      <c r="F68" s="34" t="n"/>
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Where the results are kept</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="35" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
+      <c r="F66" s="34" t="n"/>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="32" t="n"/>
+      <c r="B67" s="32" t="n"/>
+      <c r="C67" s="32" t="n"/>
+      <c r="D67" s="32" t="n"/>
+      <c r="E67" s="32" t="n"/>
+      <c r="F67" s="32" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>C.  Sign-off</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Who accepts the gap, by name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B69" s="15" t="n"/>
@@ -3527,7 +3495,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>The date by which it closes</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="B70" s="15" t="n"/>
@@ -3539,7 +3507,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>How many consecutive sign-offs have accepted this same gap</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B71" s="15" t="n"/>
@@ -3548,280 +3516,442 @@
       <c r="E71" s="36" t="n"/>
       <c r="F71" s="34" t="n"/>
     </row>
-    <row r="72" ht="26" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Version of the design document signed</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="35" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
+      <c r="F72" s="34" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Version of this record signed</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="35" t="n"/>
+      <c r="D73" s="36" t="n"/>
+      <c r="E73" s="36" t="n"/>
+      <c r="F73" s="34" t="n"/>
+    </row>
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>The risk that is left, stated in their words</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="35" t="n"/>
+      <c r="D74" s="36" t="n"/>
+      <c r="E74" s="36" t="n"/>
+      <c r="F74" s="34" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Any classification floor lowered by a compensating control</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="n"/>
+      <c r="C75" s="35" t="n"/>
+      <c r="D75" s="36" t="n"/>
+      <c r="E75" s="36" t="n"/>
+      <c r="F75" s="34" t="n"/>
+    </row>
+    <row r="76" ht="13" customHeight="1">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>A floor lowered in the design document and not repeated here has not been accepted by anybody.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="56" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Conditions on the sign-off, and when it must be looked at again</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="n"/>
+      <c r="C77" s="35" t="n"/>
+      <c r="D77" s="36" t="n"/>
+      <c r="E77" s="36" t="n"/>
+      <c r="F77" s="34" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>THE LEVEL GAP.  The agent's classification names a platform control level and a monitoring level that an agent in it requires. Where the level applied is lower, the gap is accepted here, by name, or it is not accepted at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Platform control level the classification requires, and the level applied</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="n"/>
+      <c r="C79" s="35" t="n"/>
+      <c r="D79" s="36" t="n"/>
+      <c r="E79" s="36" t="n"/>
+      <c r="F79" s="34" t="n"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Monitoring level the classification requires, and the level applied</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="35" t="n"/>
+      <c r="D80" s="36" t="n"/>
+      <c r="E80" s="36" t="n"/>
+      <c r="F80" s="34" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Who accepts the gap, by name</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="n"/>
+      <c r="C81" s="35" t="n"/>
+      <c r="D81" s="36" t="n"/>
+      <c r="E81" s="36" t="n"/>
+      <c r="F81" s="34" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>The date by which it closes</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="n"/>
+      <c r="C82" s="35" t="n"/>
+      <c r="D82" s="36" t="n"/>
+      <c r="E82" s="36" t="n"/>
+      <c r="F82" s="34" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>How many consecutive sign-offs have accepted this same gap</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="n"/>
+      <c r="C83" s="35" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="34" t="n"/>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>Answer the last row honestly. A gap accepted once is a legitimate decision made under time pressure. A gap accepted three times in a row is a decision nobody is making, and this count is the only thing on any of these forms that would show it.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="32" t="n"/>
-      <c r="B73" s="32" t="n"/>
-      <c r="C73" s="32" t="n"/>
-      <c r="D73" s="32" t="n"/>
-      <c r="E73" s="32" t="n"/>
-      <c r="F73" s="32" t="n"/>
-    </row>
-    <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="24" t="inlineStr">
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="32" t="n"/>
+      <c r="B85" s="32" t="n"/>
+      <c r="C85" s="32" t="n"/>
+      <c r="D85" s="32" t="n"/>
+      <c r="E85" s="32" t="n"/>
+      <c r="F85" s="32" t="n"/>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
         <is>
           <t>The sign-off is against the two versions named above. When live behavior stops matching the description it was granted against, it is void until somebody looks again.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="26" customHeight="1">
-      <c r="A75" s="32" t="n"/>
-      <c r="B75" s="32" t="n"/>
-      <c r="C75" s="32" t="n"/>
-      <c r="D75" s="32" t="n"/>
-      <c r="E75" s="32" t="n"/>
-      <c r="F75" s="32" t="n"/>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="32" t="n"/>
+      <c r="B87" s="32" t="n"/>
+      <c r="C87" s="32" t="n"/>
+      <c r="D87" s="32" t="n"/>
+      <c r="E87" s="32" t="n"/>
+      <c r="F87" s="32" t="n"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>D.  Revision history</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="14" t="inlineStr">
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C77" s="14" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr">
+      <c r="D89" s="14" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="E77" s="14" t="inlineStr">
+      <c r="E89" s="14" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="F89" s="14" t="inlineStr">
         <is>
           <t>Did it need a new sign-off</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="26" customHeight="1">
-      <c r="A78" s="35" t="n"/>
-      <c r="B78" s="35" t="n"/>
-      <c r="C78" s="35" t="n"/>
-      <c r="D78" s="35" t="n"/>
-      <c r="E78" s="35" t="n"/>
-      <c r="F78" s="35" t="n"/>
-    </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="35" t="n"/>
-      <c r="B79" s="35" t="n"/>
-      <c r="C79" s="35" t="n"/>
-      <c r="D79" s="35" t="n"/>
-      <c r="E79" s="35" t="n"/>
-      <c r="F79" s="35" t="n"/>
-    </row>
-    <row r="80" ht="26" customHeight="1">
-      <c r="A80" s="35" t="n"/>
-      <c r="B80" s="35" t="n"/>
-      <c r="C80" s="35" t="n"/>
-      <c r="D80" s="35" t="n"/>
-      <c r="E80" s="35" t="n"/>
-      <c r="F80" s="35" t="n"/>
-    </row>
-    <row r="81" ht="26" customHeight="1">
-      <c r="A81" s="35" t="n"/>
-      <c r="B81" s="35" t="n"/>
-      <c r="C81" s="35" t="n"/>
-      <c r="D81" s="35" t="n"/>
-      <c r="E81" s="35" t="n"/>
-      <c r="F81" s="35" t="n"/>
-    </row>
-    <row r="82" ht="26" customHeight="1">
-      <c r="A82" s="35" t="n"/>
-      <c r="B82" s="35" t="n"/>
-      <c r="C82" s="35" t="n"/>
-      <c r="D82" s="35" t="n"/>
-      <c r="E82" s="35" t="n"/>
-      <c r="F82" s="35" t="n"/>
-    </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="A83" s="35" t="n"/>
-      <c r="B83" s="35" t="n"/>
-      <c r="C83" s="35" t="n"/>
-      <c r="D83" s="35" t="n"/>
-      <c r="E83" s="35" t="n"/>
-      <c r="F83" s="35" t="n"/>
-    </row>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="35" t="n"/>
-      <c r="B84" s="35" t="n"/>
-      <c r="C84" s="35" t="n"/>
-      <c r="D84" s="35" t="n"/>
-      <c r="E84" s="35" t="n"/>
-      <c r="F84" s="35" t="n"/>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="35" t="n"/>
-      <c r="B85" s="35" t="n"/>
-      <c r="C85" s="35" t="n"/>
-      <c r="D85" s="35" t="n"/>
-      <c r="E85" s="35" t="n"/>
-      <c r="F85" s="35" t="n"/>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="35" t="n"/>
-      <c r="B86" s="35" t="n"/>
-      <c r="C86" s="35" t="n"/>
-      <c r="D86" s="35" t="n"/>
-      <c r="E86" s="35" t="n"/>
-      <c r="F86" s="35" t="n"/>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="A87" s="35" t="n"/>
-      <c r="B87" s="35" t="n"/>
-      <c r="C87" s="35" t="n"/>
-      <c r="D87" s="35" t="n"/>
-      <c r="E87" s="35" t="n"/>
-      <c r="F87" s="35" t="n"/>
-    </row>
-    <row r="88" ht="26" customHeight="1">
-      <c r="A88" s="13" t="inlineStr">
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="35" t="n"/>
+      <c r="B90" s="35" t="n"/>
+      <c r="C90" s="35" t="n"/>
+      <c r="D90" s="35" t="n"/>
+      <c r="E90" s="35" t="n"/>
+      <c r="F90" s="35" t="n"/>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="35" t="n"/>
+      <c r="B91" s="35" t="n"/>
+      <c r="C91" s="35" t="n"/>
+      <c r="D91" s="35" t="n"/>
+      <c r="E91" s="35" t="n"/>
+      <c r="F91" s="35" t="n"/>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="35" t="n"/>
+      <c r="B92" s="35" t="n"/>
+      <c r="C92" s="35" t="n"/>
+      <c r="D92" s="35" t="n"/>
+      <c r="E92" s="35" t="n"/>
+      <c r="F92" s="35" t="n"/>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="35" t="n"/>
+      <c r="B93" s="35" t="n"/>
+      <c r="C93" s="35" t="n"/>
+      <c r="D93" s="35" t="n"/>
+      <c r="E93" s="35" t="n"/>
+      <c r="F93" s="35" t="n"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="35" t="n"/>
+      <c r="B94" s="35" t="n"/>
+      <c r="C94" s="35" t="n"/>
+      <c r="D94" s="35" t="n"/>
+      <c r="E94" s="35" t="n"/>
+      <c r="F94" s="35" t="n"/>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="35" t="n"/>
+      <c r="B95" s="35" t="n"/>
+      <c r="C95" s="35" t="n"/>
+      <c r="D95" s="35" t="n"/>
+      <c r="E95" s="35" t="n"/>
+      <c r="F95" s="35" t="n"/>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="35" t="n"/>
+      <c r="B96" s="35" t="n"/>
+      <c r="C96" s="35" t="n"/>
+      <c r="D96" s="35" t="n"/>
+      <c r="E96" s="35" t="n"/>
+      <c r="F96" s="35" t="n"/>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="35" t="n"/>
+      <c r="B97" s="35" t="n"/>
+      <c r="C97" s="35" t="n"/>
+      <c r="D97" s="35" t="n"/>
+      <c r="E97" s="35" t="n"/>
+      <c r="F97" s="35" t="n"/>
+    </row>
+    <row r="98" ht="26" customHeight="1">
+      <c r="A98" s="35" t="n"/>
+      <c r="B98" s="35" t="n"/>
+      <c r="C98" s="35" t="n"/>
+      <c r="D98" s="35" t="n"/>
+      <c r="E98" s="35" t="n"/>
+      <c r="F98" s="35" t="n"/>
+    </row>
+    <row r="99" ht="26" customHeight="1">
+      <c r="A99" s="35" t="n"/>
+      <c r="B99" s="35" t="n"/>
+      <c r="C99" s="35" t="n"/>
+      <c r="D99" s="35" t="n"/>
+      <c r="E99" s="35" t="n"/>
+      <c r="F99" s="35" t="n"/>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="13" t="inlineStr">
         <is>
           <t>A model version bump, a framework upgrade, a new tool, or a change of host all produce a row. Answer the last column every time, because an auditor will ask which changes went live without a fresh sign-off.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="109">
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C61:F61"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <mergeCells count="131">
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="C11:F11"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="C63:F63"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C67:F67"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="A69:B69"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:F52"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C65:F65"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A58:B58"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation sqref="D34:D45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Wider,Narrower,The same"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E34:E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Gateway,Policy engine,Scoped credential,Tool wrapper,Nowhere"</formula1>
+    </dataValidation>
     <dataValidation sqref="C16 C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Level 1 — Hand-scoped,Level 2 — Classification ceiling,Level 3 — Policy as code"</formula1>
     </dataValidation>
-    <dataValidation sqref="F78:F87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F90:F99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -961,7 +961,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
@@ -1878,7 +1878,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="103">
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A73:B73"/>
@@ -2388,7 +2388,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="32">
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="E12:F12"/>
@@ -2789,7 +2789,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="5">
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
@@ -5103,7 +5103,7 @@
       <c r="F99" s="34" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="116">
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="E62:F62"/>
@@ -6294,7 +6294,7 @@
       <c r="F103" s="34" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="120">
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="E62:F62"/>
@@ -6983,7 +6983,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="8">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Agent Design" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Classification" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2a Floor Anchors" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Platform &amp; Sign-off" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Monitoring" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Audit &amp; Assurance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1 Agent Design" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2 Classification" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2a Floor Anchors" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3 Platform &amp; Sign-off" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4 Monitoring" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5 Audit &amp; Assurance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6 Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Agent Design'!$1:$2</definedName>
@@ -412,39 +412,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1714500" cy="771525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -972,7 +939,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -982,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1346,7 +1312,7 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Can the action be undone, and within what window</t>
+          <t>Can the action be undone, by whom, and within what window</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -1494,7 +1460,7 @@
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="34" t="n"/>
     </row>
-    <row r="49" ht="70" customHeight="70">
+    <row r="49" ht="70" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
           <t>The most money or value the agent can move in one action, and in one day, stated for each kind of movement it can make: money out (payments, refunds, credits, discounts), money in (charges, invoices, collections), and commitments that become money later (orders, contracts, billable provisioning). Value that is not currency counts: inventory, store credit, points, gift cards, licences. Write "none" against a kind that has no ceiling, and expect the Classification sheet to charge you for it.</t>
@@ -1517,7 +1483,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" ht="56" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Action or decision</t>
@@ -1525,7 +1491,7 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Alone, never, or needs approval</t>
+          <t>Never, needs a person to approve, alone and reviewed afterwards, or alone and unreviewed</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -1610,202 +1576,200 @@
       <c r="F60" s="36" t="n"/>
       <c r="G60" s="34" t="n"/>
     </row>
-    <row r="61" ht="14" customHeight="1">
+    <row r="61" ht="40" customHeight="1">
       <c r="A61" s="13" t="inlineStr">
         <is>
+          <t>The middle column takes four answers: may never do, needs a person to approve, alone and a person sees the result afterwards, or alone and nobody sees it unless something alerts. The last three are question 7's Routine, Sensitive and Critical anchors. Question 7 is answered for the agent and not for one row, so read the whole column and take the highest anchor any row reaches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
           <t>Enforcement is one of four answers: in the prompt, in the tool layer, in the platform, or nowhere. "In the prompt" counts, and it is the weakest of the four.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="83" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="63" ht="83" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>If any row above says "In the prompt", say how the prompt is controlled. Where it lives, who can change it, and whether a change is reviewed before it reaches production. A control written into a prompt that anybody can edit is not a weak control, it is a removable one, and nothing in section 7 will show you that it went.</t>
         </is>
       </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="35" t="n"/>
-      <c r="D62" s="36" t="n"/>
-      <c r="E62" s="36" t="n"/>
-      <c r="F62" s="36" t="n"/>
-      <c r="G62" s="34" t="n"/>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="32" t="n"/>
-      <c r="B63" s="32" t="n"/>
-      <c r="C63" s="32" t="n"/>
-      <c r="D63" s="32" t="n"/>
-      <c r="E63" s="32" t="n"/>
-      <c r="F63" s="32" t="n"/>
-      <c r="G63" s="32" t="n"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="35" t="n"/>
+      <c r="D63" s="36" t="n"/>
+      <c r="E63" s="36" t="n"/>
+      <c r="F63" s="36" t="n"/>
+      <c r="G63" s="34" t="n"/>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="32" t="n"/>
+      <c r="B64" s="32" t="n"/>
+      <c r="C64" s="32" t="n"/>
+      <c r="D64" s="32" t="n"/>
+      <c r="E64" s="32" t="n"/>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>5.  Escalation and override</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="56" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="66" ht="56" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>How the agent hands work to a person</t>
         </is>
       </c>
-      <c r="B65" s="15" t="n"/>
-      <c r="C65" s="35" t="n"/>
-      <c r="D65" s="36" t="n"/>
-      <c r="E65" s="36" t="n"/>
-      <c r="F65" s="36" t="n"/>
-      <c r="G65" s="34" t="n"/>
-    </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="35" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
+      <c r="F66" s="36" t="n"/>
+      <c r="G66" s="34" t="n"/>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>What triggers it, who receives it, in which channel, and what happens if nobody answers.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="56" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="68" ht="56" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>How a person stops the agent</t>
         </is>
       </c>
-      <c r="B67" s="15" t="n"/>
-      <c r="C67" s="35" t="n"/>
-      <c r="D67" s="36" t="n"/>
-      <c r="E67" s="36" t="n"/>
-      <c r="F67" s="36" t="n"/>
-      <c r="G67" s="34" t="n"/>
-    </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="35" t="n"/>
+      <c r="D68" s="36" t="n"/>
+      <c r="E68" s="36" t="n"/>
+      <c r="F68" s="36" t="n"/>
+      <c r="G68" s="34" t="n"/>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>The specific action, who can take it, and how long it takes to have effect. Include how a run already in progress is stopped.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="56" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+    <row r="70" ht="56" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>How a person reverses what it already did</t>
         </is>
       </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="35" t="n"/>
-      <c r="D69" s="36" t="n"/>
-      <c r="E69" s="36" t="n"/>
-      <c r="F69" s="36" t="n"/>
-      <c r="G69" s="34" t="n"/>
-    </row>
-    <row r="70" ht="13" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="35" t="n"/>
+      <c r="D70" s="36" t="n"/>
+      <c r="E70" s="36" t="n"/>
+      <c r="F70" s="36" t="n"/>
+      <c r="G70" s="34" t="n"/>
+    </row>
+    <row r="71" ht="13" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Per row of section 3 where the answer differs.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="56" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
+    <row r="72" ht="56" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>How the person on the other end challenges what it did</t>
         </is>
       </c>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="35" t="n"/>
-      <c r="D71" s="36" t="n"/>
-      <c r="E71" s="36" t="n"/>
-      <c r="F71" s="36" t="n"/>
-      <c r="G71" s="34" t="n"/>
-    </row>
-    <row r="72" ht="13" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="35" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
+      <c r="F72" s="36" t="n"/>
+      <c r="G72" s="34" t="n"/>
+    </row>
+    <row r="73" ht="13" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>For any agent whose audience is not internal staff. Who they raise it with, how a person looks at the decision again, and where that gets recorded.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="56" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Who is told when it fails</t>
         </is>
       </c>
-      <c r="B73" s="15" t="n"/>
-      <c r="C73" s="35" t="n"/>
-      <c r="D73" s="36" t="n"/>
-      <c r="E73" s="36" t="n"/>
-      <c r="F73" s="36" t="n"/>
-      <c r="G73" s="34" t="n"/>
-    </row>
-    <row r="74" ht="13" customHeight="1">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="35" t="n"/>
+      <c r="D74" s="36" t="n"/>
+      <c r="E74" s="36" t="n"/>
+      <c r="F74" s="36" t="n"/>
+      <c r="G74" s="34" t="n"/>
+    </row>
+    <row r="75" ht="13" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>The person, the channel, and the time within which they are told.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="26" customHeight="1">
-      <c r="A75" s="32" t="n"/>
-      <c r="B75" s="32" t="n"/>
-      <c r="C75" s="32" t="n"/>
-      <c r="D75" s="32" t="n"/>
-      <c r="E75" s="32" t="n"/>
-      <c r="F75" s="32" t="n"/>
-      <c r="G75" s="32" t="n"/>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>6.  Classification and the Classification Test  →  see the Classification sheet</t>
-        </is>
-      </c>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="32" t="n"/>
+      <c r="B76" s="32" t="n"/>
+      <c r="C76" s="32" t="n"/>
+      <c r="D76" s="32" t="n"/>
+      <c r="E76" s="32" t="n"/>
+      <c r="F76" s="32" t="n"/>
+      <c r="G76" s="32" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
+          <t>6.  Classification and the Classification Test  →  see the Classification sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
           <t>7.  Revision history</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="14" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="E78" s="14" t="inlineStr">
+      <c r="E79" s="14" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="F78" s="15" t="n"/>
-      <c r="G78" s="14" t="n"/>
-    </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="35" t="n"/>
-      <c r="B79" s="35" t="n"/>
-      <c r="C79" s="35" t="n"/>
-      <c r="D79" s="35" t="n"/>
-      <c r="E79" s="35" t="n"/>
-      <c r="F79" s="34" t="n"/>
-      <c r="G79" s="35" t="n"/>
+      <c r="F79" s="15" t="n"/>
+      <c r="G79" s="14" t="n"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="35" t="n"/>
@@ -1870,8 +1834,17 @@
       <c r="F86" s="34" t="n"/>
       <c r="G86" s="35" t="n"/>
     </row>
-    <row r="87" ht="39" customHeight="1">
-      <c r="A87" s="13" t="inlineStr">
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="35" t="n"/>
+      <c r="B87" s="35" t="n"/>
+      <c r="C87" s="35" t="n"/>
+      <c r="D87" s="35" t="n"/>
+      <c r="E87" s="35" t="n"/>
+      <c r="F87" s="34" t="n"/>
+      <c r="G87" s="35" t="n"/>
+    </row>
+    <row r="88" ht="39" customHeight="1">
+      <c r="A88" s="13" t="inlineStr">
         <is>
           <t>One more tool, a widened scope, or a new audience all produce a row. So do stage 4 and stage 5 findings: an eval that catches drift, an audit finding against your classification criteria, or a monitor reporting a tool call outside section 3. A new model version does not; that changes the Platform and Sign-off Record instead. Retiring the agent produces the last row: set Status above to retired, date it, and fill in section E of the Audit &amp; Assurance sheet.</t>
         </is>
@@ -1879,29 +1852,30 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="103">
+  <mergeCells count="104">
+    <mergeCell ref="C68:G68"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A73:B73"/>
     <mergeCell ref="C58:G58"/>
+    <mergeCell ref="A62:G62"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C45:G45"/>
-    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E87:F87"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C65:G65"/>
     <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="C60:G60"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="C71:G71"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A62:B62"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="E85:F85"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C57:G57"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A71:G71"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A48:B48"/>
@@ -1921,67 +1895,67 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C46:G46"/>
-    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C70:G70"/>
     <mergeCell ref="C48:G48"/>
+    <mergeCell ref="A75:G75"/>
     <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="E83:F83"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C74:G74"/>
     <mergeCell ref="C26:G26"/>
-    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A67:G67"/>
     <mergeCell ref="C16:G16"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C55:G55"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="E84:F84"/>
-    <mergeCell ref="E78:F78"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="E86:F86"/>
     <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="C52:G52"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
     <mergeCell ref="E81:F81"/>
     <mergeCell ref="C28:G28"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C69:G69"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E82:F82"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="C73:G73"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="A66:B66"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A73:G73"/>
     <mergeCell ref="F41:G41"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="C56:G56"/>
     <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A88:G88"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="C66:G66"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A76:G76"/>
     <mergeCell ref="A33:G33"/>
   </mergeCells>
   <dataValidations count="4">
@@ -1992,7 +1966,7 @@
       <formula1>"Tool level,Data level,Not enforceable here"</formula1>
     </dataValidation>
     <dataValidation sqref="B53:B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"May do alone,May never do,Needs a person to approve"</formula1>
+      <formula1>"May never do,Needs a person to approve,Alone — a person sees the result afterwards,Alone — nobody sees it unless something alerts"</formula1>
     </dataValidation>
     <dataValidation sqref="C53:C60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"In the platform,In the tool layer,In the prompt,Nowhere"</formula1>
@@ -2179,7 +2153,7 @@
       <c r="E13" s="35" t="n"/>
       <c r="F13" s="34" t="n"/>
     </row>
-    <row r="14" ht="48" customHeight="48">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="17" t="n">
         <v>4</v>
       </c>
@@ -2255,11 +2229,6 @@
           <t>Question 3 is not a question this form answers, and not one the agent’s team answers on its own. Which regulations reach a process is a determination from whoever advises your company on regulation — legal, compliance, or privacy. Record their answer in the row and name them; "none that we have identified" with nobody named behind it leaves the row unanswered.</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="32" t="n"/>
@@ -2390,7 +2359,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="32">
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A27:F27"/>
@@ -2411,6 +2379,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="E11:F11"/>
@@ -2774,7 +2743,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="100" customHeight="100">
+    <row r="17" ht="100" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Question 4 covers three kinds of movement, and most agents that reach it do more than one: money out (paying, refunding, crediting, discounting), money in (charging, invoicing, collecting) and commitments that become money later (orders, contracts, billable provisioning). Value that is not currency counts on the same footing: inventory, store credit, points, gift cards, licences. Answer for every kind the agent can do, name a ceiling for each, and take the highest floor any of them sets. Question 4 sets no amount, and this pack names none. What a given agent may move is the value ceiling in section 3 of its Agent Design sheet, accepted by whoever signs it off. The anchors judge the shape of the control instead: whether a ceiling exists, whether it covers a day as well as an action, and whether the platform enforces it or the agent is trusted to observe it. Question 7 is the one row where the anchors describe supervision instead of damage: it is what turns the other seven into risk.</t>
@@ -2807,7 +2776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2918,7 +2887,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Model provider, and where inference happens</t>
+          <t>Is that model version pinned, or does it float</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -2927,22 +2896,17 @@
       <c r="E11" s="36" t="n"/>
       <c r="F11" s="34" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Agent framework, and its version</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="34" t="n"/>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>A floating alias changes the model underneath this record: no row in section D, no re-test, and the record still reads as accurate. Carry a floating answer into section C as remaining risk.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Where it is hosted</t>
+          <t>Model provider, and where inference happens</t>
         </is>
       </c>
       <c r="B13" s="15" t="n"/>
@@ -2954,7 +2918,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Agent login: the identity it uses, and what else uses that identity</t>
+          <t>Agent framework, and its version</t>
         </is>
       </c>
       <c r="B14" s="15" t="n"/>
@@ -2966,7 +2930,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>How the credentials are revoked, by whom, and how long that takes, measured to the point the existing credentials stop working</t>
+          <t>Where it is hosted</t>
         </is>
       </c>
       <c r="B15" s="15" t="n"/>
@@ -2978,7 +2942,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Platform control level of the platform it runs on</t>
+          <t>Agent login: the identity it uses, and what else uses that identity</t>
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
@@ -2987,22 +2951,22 @@
       <c r="E16" s="36" t="n"/>
       <c r="F16" s="34" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Level 1 Hand-scoped, Level 2 Classification ceiling, Level 3 Policy as code. Defined in your Platform Control Levels.</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>How the credentials are revoked, by whom, and how long that takes, measured to the point the existing credentials stop working</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="34" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Platform control level actually applied to this agent</t>
+          <t>Platform control level of the platform it runs on</t>
         </is>
       </c>
       <c r="B18" s="15" t="n"/>
@@ -3011,17 +2975,22 @@
       <c r="E18" s="36" t="n"/>
       <c r="F18" s="34" t="n"/>
     </row>
-    <row r="19" ht="13" customHeight="1">
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Can be lower than the platform's. It cannot be higher.</t>
-        </is>
-      </c>
+          <t>Level 1 Hand-scoped, Level 2 Classification ceiling, Level 3 Policy as code. Defined in your Platform Control Levels.</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Version of the Platform Control Levels this score was made against</t>
+          <t>Platform control level actually applied to this agent</t>
         </is>
       </c>
       <c r="B20" s="15" t="n"/>
@@ -3030,29 +2999,29 @@
       <c r="E20" s="36" t="n"/>
       <c r="F20" s="34" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>When this agent's access is reviewed again, and by whom</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="34" t="n"/>
-    </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Permissions are granted once and then survive every later change to what the agent does.</t>
-        </is>
-      </c>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Can be lower than the platform's. It cannot be higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Version of the Platform Control Levels this score was made against</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="34" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Autonomy level, on the four-level scale in the CSA agentic profile, or your own if you keep one</t>
+          <t>When this agent's access is reviewed again, and by whom</t>
         </is>
       </c>
       <c r="B23" s="15" t="n"/>
@@ -3064,14 +3033,14 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Recorded here, never as the classification.</t>
+          <t>Permissions are granted once and then survive every later change to what the agent does.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Tool servers and connectors it reaches, and who publishes each one</t>
+          <t>Autonomy level, on the four-level scale in the CSA agentic profile, or your own if you keep one</t>
         </is>
       </c>
       <c r="B25" s="15" t="n"/>
@@ -3083,103 +3052,106 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
+          <t>Recorded here, never as the classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Tool servers and connectors it reaches, and who publishes each one</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="34" t="n"/>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
           <t>An MCP server or a shared connector is a dependency the agent inherits, published by somebody who can change it without telling you.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="32" t="n"/>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-    </row>
-    <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="32" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="32" t="n"/>
+      <c r="E29" s="32" t="n"/>
+      <c r="F29" s="32" t="n"/>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Where the grant list is enforced</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="35" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="34" t="n"/>
-    </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="34" t="n"/>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Section 3 of the design document lists the tools and the data. Name the component that enforces it: a gateway, a policy engine, scoped credentials, or a tool wrapper.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="32" t="n"/>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="32" t="n"/>
+      <c r="B32" s="32" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>What was actually granted, row by row</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="15" t="n"/>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Take each row of section 3 and write the permission that was really created for it, using the exact name your platform uses. This is the list your monitor compares live tool calls against.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Row in section 3</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>The permission actually granted, as the platform names it</t>
         </is>
       </c>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>Wider, narrower, or the same</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Where it is enforced</t>
         </is>
       </c>
-      <c r="F33" s="15" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="35" t="n"/>
-      <c r="B34" s="35" t="n"/>
-      <c r="C34" s="34" t="n"/>
-      <c r="D34" s="35" t="n"/>
-      <c r="E34" s="35" t="n"/>
-      <c r="F34" s="34" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="35" t="n"/>
-      <c r="B35" s="35" t="n"/>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="35" t="n"/>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="34" t="n"/>
+      <c r="F35" s="15" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="35" t="n"/>
@@ -3261,44 +3233,41 @@
       <c r="E45" s="35" t="n"/>
       <c r="F45" s="34" t="n"/>
     </row>
-    <row r="46" ht="54" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="35" t="n"/>
+      <c r="B46" s="35" t="n"/>
+      <c r="C46" s="34" t="n"/>
+      <c r="D46" s="35" t="n"/>
+      <c r="E46" s="35" t="n"/>
+      <c r="F46" s="34" t="n"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="35" t="n"/>
+      <c r="B47" s="35" t="n"/>
+      <c r="C47" s="34" t="n"/>
+      <c r="D47" s="35" t="n"/>
+      <c r="E47" s="35" t="n"/>
+      <c r="F47" s="34" t="n"/>
+    </row>
+    <row r="48" ht="54" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Add rows until every row of section 3 has one here — select a row inside the table and insert, then copy an existing row down so the dropdowns come with it. A summary of thirty grants is not this table. "Nowhere" in the last column is an honest answer: the row is a sentence in a document rather than a control, and it belongs in section C as remaining risk.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="32" t="n"/>
-      <c r="B47" s="32" t="n"/>
-      <c r="C47" s="32" t="n"/>
-      <c r="D47" s="32" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-    </row>
-    <row r="48" ht="56" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Anything narrower than the design document asks for</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="34" t="n"/>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>Say what the agent cannot do as a result, and whether anybody has worked around it.</t>
-        </is>
-      </c>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="32" t="n"/>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="32" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
     </row>
     <row r="50" ht="56" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>What is granted that the design document does not list</t>
+          <t>Anything narrower than the design document asks for</t>
         </is>
       </c>
       <c r="B50" s="15" t="n"/>
@@ -3307,17 +3276,17 @@
       <c r="E50" s="36" t="n"/>
       <c r="F50" s="34" t="n"/>
     </row>
-    <row r="51" ht="27" customHeight="1">
+    <row r="51" ht="13" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Anything the agent can reach that section 3 does not name. This should be empty. Where it is not, carry it into section C as remaining risk. Do not fix it quietly and leave this blank.</t>
+          <t>Say what the agent cannot do as a result, and whether anybody has worked around it.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="56" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Limits the platform cannot express</t>
+          <t>What is granted that the design document does not list</t>
         </is>
       </c>
       <c r="B52" s="15" t="n"/>
@@ -3326,63 +3295,63 @@
       <c r="E52" s="36" t="n"/>
       <c r="F52" s="34" t="n"/>
     </row>
-    <row r="53" ht="40" customHeight="1">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
+          <t>Anything the agent can reach that section 3 does not name. This should be empty. Where it is not, carry it into section C as remaining risk. Do not fix it quietly and leave this blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="56" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Limits the platform cannot express</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n"/>
+      <c r="C54" s="35" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="34" t="n"/>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
           <t>Every row of section 3 whose granularity is "not enforceable here": a boundary declared in stage 1 that nothing here can hold. Say what the agent can reach as a result, and carry these into section C as remaining risk. The row above is access nobody meant to grant; this one is a limit nobody can enforce.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="32" t="n"/>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="32" t="n"/>
-      <c r="F54" s="32" t="n"/>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="32" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="32" t="n"/>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>B.  What the evals found   (against the setup in section A, not a development configuration)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Which evals you ran</t>
         </is>
       </c>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="35" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-      <c r="F56" s="34" t="n"/>
-    </row>
-    <row r="57" ht="56" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="35" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="36" t="n"/>
+      <c r="F58" s="34" t="n"/>
+    </row>
+    <row r="59" ht="56" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Adversarial testing performed, and what it was tested against</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n"/>
-      <c r="C57" s="35" t="n"/>
-      <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="n"/>
-      <c r="F57" s="34" t="n"/>
-    </row>
-    <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>For any agent that reads content it did not author, whether it can be talked into something is what the sign-off most needs to know. Name what you tested against from OWASP's Top 10 for Agentic Applications, the same list the Monitoring sheet's playbook works from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Against which configuration, matching section A</t>
         </is>
       </c>
       <c r="B59" s="15" t="n"/>
@@ -3391,22 +3360,17 @@
       <c r="E59" s="36" t="n"/>
       <c r="F59" s="34" t="n"/>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="35" t="n"/>
-      <c r="D60" s="36" t="n"/>
-      <c r="E60" s="36" t="n"/>
-      <c r="F60" s="34" t="n"/>
-    </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>For any agent that reads content it did not author, whether it can be talked into something is what the sign-off most needs to know. Name what you tested against from OWASP's Top 10 for Agentic Applications, the same list the Monitoring sheet's playbook works from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>What they found</t>
+          <t>Against which configuration, matching section A</t>
         </is>
       </c>
       <c r="B61" s="15" t="n"/>
@@ -3415,17 +3379,22 @@
       <c r="E61" s="36" t="n"/>
       <c r="F61" s="34" t="n"/>
     </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>This is what the person signing off is accepting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="35" t="n"/>
+      <c r="D62" s="36" t="n"/>
+      <c r="E62" s="36" t="n"/>
+      <c r="F62" s="34" t="n"/>
+    </row>
+    <row r="63" ht="56" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>What you changed because of it</t>
+          <t>What they found</t>
         </is>
       </c>
       <c r="B63" s="15" t="n"/>
@@ -3434,29 +3403,29 @@
       <c r="E63" s="36" t="n"/>
       <c r="F63" s="34" t="n"/>
     </row>
-    <row r="64" ht="56" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>What you know you did NOT test</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="n"/>
-      <c r="C64" s="35" t="n"/>
-      <c r="D64" s="36" t="n"/>
-      <c r="E64" s="36" t="n"/>
-      <c r="F64" s="34" t="n"/>
-    </row>
-    <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>This is where stage 4 monitoring has to begin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>This is what the person signing off is accepting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>What you changed because of it</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="35" t="n"/>
+      <c r="D65" s="36" t="n"/>
+      <c r="E65" s="36" t="n"/>
+      <c r="F65" s="34" t="n"/>
+    </row>
+    <row r="66" ht="56" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Where the results are kept</t>
+          <t>Which rows of section 3 and section 4 the evals exercised, and which they did not</t>
         </is>
       </c>
       <c r="B66" s="15" t="n"/>
@@ -3466,36 +3435,35 @@
       <c r="F66" s="34" t="n"/>
     </row>
     <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="32" t="n"/>
-      <c r="B67" s="32" t="n"/>
-      <c r="C67" s="32" t="n"/>
-      <c r="D67" s="32" t="n"/>
-      <c r="E67" s="32" t="n"/>
-      <c r="F67" s="32" t="n"/>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>C.  Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="35" t="n"/>
-      <c r="D69" s="36" t="n"/>
-      <c r="E69" s="36" t="n"/>
-      <c r="F69" s="34" t="n"/>
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>Name them the way those sections name them. Twelve grants and four decisions tested on two grants and no decisions passes this section otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="56" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>What you know you did NOT test</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="35" t="n"/>
+      <c r="D68" s="36" t="n"/>
+      <c r="E68" s="36" t="n"/>
+      <c r="F68" s="34" t="n"/>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>This is where stage 4 monitoring has to begin.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Where the results are kept</t>
         </is>
       </c>
       <c r="B70" s="15" t="n"/>
@@ -3504,34 +3472,25 @@
       <c r="E70" s="36" t="n"/>
       <c r="F70" s="34" t="n"/>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="35" t="n"/>
-      <c r="D71" s="36" t="n"/>
-      <c r="E71" s="36" t="n"/>
-      <c r="F71" s="34" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>Version of the design document signed</t>
-        </is>
-      </c>
-      <c r="B72" s="15" t="n"/>
-      <c r="C72" s="35" t="n"/>
-      <c r="D72" s="36" t="n"/>
-      <c r="E72" s="36" t="n"/>
-      <c r="F72" s="34" t="n"/>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="32" t="n"/>
+      <c r="B71" s="32" t="n"/>
+      <c r="C71" s="32" t="n"/>
+      <c r="D71" s="32" t="n"/>
+      <c r="E71" s="32" t="n"/>
+      <c r="F71" s="32" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>C.  Sign-off</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Version of this record signed</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B73" s="15" t="n"/>
@@ -3540,10 +3499,10 @@
       <c r="E73" s="36" t="n"/>
       <c r="F73" s="34" t="n"/>
     </row>
-    <row r="74" ht="56" customHeight="1">
+    <row r="74" ht="30" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>The risk that is left, stated in their words</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="B74" s="15" t="n"/>
@@ -3555,7 +3514,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Any classification floor lowered by a compensating control</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B75" s="15" t="n"/>
@@ -3564,17 +3523,22 @@
       <c r="E75" s="36" t="n"/>
       <c r="F75" s="34" t="n"/>
     </row>
-    <row r="76" ht="13" customHeight="1">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>A floor lowered in the design document and not repeated here has not been accepted by anybody.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="56" customHeight="1">
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Version of the design document signed</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="35" t="n"/>
+      <c r="D76" s="36" t="n"/>
+      <c r="E76" s="36" t="n"/>
+      <c r="F76" s="34" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Conditions on the sign-off, and when it must be looked at again</t>
+          <t>Version of this record signed</t>
         </is>
       </c>
       <c r="B77" s="15" t="n"/>
@@ -3583,17 +3547,22 @@
       <c r="E77" s="36" t="n"/>
       <c r="F77" s="34" t="n"/>
     </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="24" t="inlineStr">
-        <is>
-          <t>THE LEVEL GAP.  The agent's classification names a platform control level and a monitoring level that an agent in it requires. Where the level applied is lower, the gap is accepted here, by name, or it is not accepted at all.</t>
-        </is>
-      </c>
+    <row r="78" ht="56" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>The risk that is left, stated in their words</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n"/>
+      <c r="C78" s="35" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="34" t="n"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Platform control level the classification requires, and the level applied</t>
+          <t>Any classification floor lowered by a compensating control</t>
         </is>
       </c>
       <c r="B79" s="15" t="n"/>
@@ -3602,22 +3571,17 @@
       <c r="E79" s="36" t="n"/>
       <c r="F79" s="34" t="n"/>
     </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Monitoring level the classification requires, and the level applied</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="n"/>
-      <c r="C80" s="35" t="n"/>
-      <c r="D80" s="36" t="n"/>
-      <c r="E80" s="36" t="n"/>
-      <c r="F80" s="34" t="n"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
+    <row r="80" ht="13" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>A floor lowered in the design document and not repeated here has not been accepted by anybody.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="56" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Who accepts the gap, by name</t>
+          <t>Conditions on the sign-off, and when it must be looked at again</t>
         </is>
       </c>
       <c r="B81" s="15" t="n"/>
@@ -3626,10 +3590,10 @@
       <c r="E81" s="36" t="n"/>
       <c r="F81" s="34" t="n"/>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="56" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>The date by which it closes</t>
+          <t>Who can change this configuration after sign-off, and what review that change gets</t>
         </is>
       </c>
       <c r="B82" s="15" t="n"/>
@@ -3638,150 +3602,167 @@
       <c r="E82" s="36" t="n"/>
       <c r="F82" s="34" t="n"/>
     </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>Section D records a change once it has happened, and only when whoever made it writes the row. This says who was permitted to make it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>What prevents deployment without this signature</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="n"/>
+      <c r="C84" s="35" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="34" t="n"/>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>This record says nothing goes live without it, and until one of the first three answers is true that is a control written into a document. "Nothing" is honest, and it belongs in the risk that is left above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>THE LEVEL GAP.  The agent's classification names a platform control level and a monitoring level that an agent in it requires. Where the level applied is lower, the gap is accepted here, by name, or it is not accepted at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Platform control level the classification requires, and the level applied</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="n"/>
+      <c r="C87" s="35" t="n"/>
+      <c r="D87" s="36" t="n"/>
+      <c r="E87" s="36" t="n"/>
+      <c r="F87" s="34" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Monitoring level the classification requires, and the level applied</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="35" t="n"/>
+      <c r="D88" s="36" t="n"/>
+      <c r="E88" s="36" t="n"/>
+      <c r="F88" s="34" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Who accepts the gap, by name</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="n"/>
+      <c r="C89" s="35" t="n"/>
+      <c r="D89" s="36" t="n"/>
+      <c r="E89" s="36" t="n"/>
+      <c r="F89" s="34" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>The date by which it closes</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n"/>
+      <c r="C90" s="35" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
+      <c r="F90" s="34" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>How many consecutive sign-offs have accepted this same gap</t>
         </is>
       </c>
-      <c r="B83" s="15" t="n"/>
-      <c r="C83" s="35" t="n"/>
-      <c r="D83" s="36" t="n"/>
-      <c r="E83" s="36" t="n"/>
-      <c r="F83" s="34" t="n"/>
-    </row>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="13" t="inlineStr">
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="35" t="n"/>
+      <c r="D91" s="36" t="n"/>
+      <c r="E91" s="36" t="n"/>
+      <c r="F91" s="34" t="n"/>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
         <is>
           <t>Answer the last row honestly. A gap accepted once is a legitimate decision made under time pressure. A gap accepted three times in a row is a decision nobody is making, and this count is the only thing on any of these forms that would show it.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="32" t="n"/>
-      <c r="B85" s="32" t="n"/>
-      <c r="C85" s="32" t="n"/>
-      <c r="D85" s="32" t="n"/>
-      <c r="E85" s="32" t="n"/>
-      <c r="F85" s="32" t="n"/>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="32" t="n"/>
+      <c r="B93" s="32" t="n"/>
+      <c r="C93" s="32" t="n"/>
+      <c r="D93" s="32" t="n"/>
+      <c r="E93" s="32" t="n"/>
+      <c r="F93" s="32" t="n"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
         <is>
           <t>The sign-off is against the two versions named above. When live behavior stops matching the description it was granted against, it is void until somebody looks again.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="A87" s="32" t="n"/>
-      <c r="B87" s="32" t="n"/>
-      <c r="C87" s="32" t="n"/>
-      <c r="D87" s="32" t="n"/>
-      <c r="E87" s="32" t="n"/>
-      <c r="F87" s="32" t="n"/>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="9" t="inlineStr">
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="32" t="n"/>
+      <c r="B95" s="32" t="n"/>
+      <c r="C95" s="32" t="n"/>
+      <c r="D95" s="32" t="n"/>
+      <c r="E95" s="32" t="n"/>
+      <c r="F95" s="32" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>D.  Revision history</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="A89" s="14" t="inlineStr">
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C89" s="14" t="inlineStr">
+      <c r="C97" s="14" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="D97" s="14" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="E89" s="14" t="inlineStr">
+      <c r="E97" s="14" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="F89" s="14" t="inlineStr">
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>Did it need a new sign-off</t>
         </is>
       </c>
-    </row>
-    <row r="90" ht="26" customHeight="1">
-      <c r="A90" s="35" t="n"/>
-      <c r="B90" s="35" t="n"/>
-      <c r="C90" s="35" t="n"/>
-      <c r="D90" s="35" t="n"/>
-      <c r="E90" s="35" t="n"/>
-      <c r="F90" s="35" t="n"/>
-    </row>
-    <row r="91" ht="26" customHeight="1">
-      <c r="A91" s="35" t="n"/>
-      <c r="B91" s="35" t="n"/>
-      <c r="C91" s="35" t="n"/>
-      <c r="D91" s="35" t="n"/>
-      <c r="E91" s="35" t="n"/>
-      <c r="F91" s="35" t="n"/>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="A92" s="35" t="n"/>
-      <c r="B92" s="35" t="n"/>
-      <c r="C92" s="35" t="n"/>
-      <c r="D92" s="35" t="n"/>
-      <c r="E92" s="35" t="n"/>
-      <c r="F92" s="35" t="n"/>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="35" t="n"/>
-      <c r="B93" s="35" t="n"/>
-      <c r="C93" s="35" t="n"/>
-      <c r="D93" s="35" t="n"/>
-      <c r="E93" s="35" t="n"/>
-      <c r="F93" s="35" t="n"/>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="A94" s="35" t="n"/>
-      <c r="B94" s="35" t="n"/>
-      <c r="C94" s="35" t="n"/>
-      <c r="D94" s="35" t="n"/>
-      <c r="E94" s="35" t="n"/>
-      <c r="F94" s="35" t="n"/>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="A95" s="35" t="n"/>
-      <c r="B95" s="35" t="n"/>
-      <c r="C95" s="35" t="n"/>
-      <c r="D95" s="35" t="n"/>
-      <c r="E95" s="35" t="n"/>
-      <c r="F95" s="35" t="n"/>
-    </row>
-    <row r="96" ht="26" customHeight="1">
-      <c r="A96" s="35" t="n"/>
-      <c r="B96" s="35" t="n"/>
-      <c r="C96" s="35" t="n"/>
-      <c r="D96" s="35" t="n"/>
-      <c r="E96" s="35" t="n"/>
-      <c r="F96" s="35" t="n"/>
-    </row>
-    <row r="97" ht="26" customHeight="1">
-      <c r="A97" s="35" t="n"/>
-      <c r="B97" s="35" t="n"/>
-      <c r="C97" s="35" t="n"/>
-      <c r="D97" s="35" t="n"/>
-      <c r="E97" s="35" t="n"/>
-      <c r="F97" s="35" t="n"/>
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="35" t="n"/>
@@ -3800,7 +3781,71 @@
       <c r="F99" s="35" t="n"/>
     </row>
     <row r="100" ht="26" customHeight="1">
-      <c r="A100" s="13" t="inlineStr">
+      <c r="A100" s="35" t="n"/>
+      <c r="B100" s="35" t="n"/>
+      <c r="C100" s="35" t="n"/>
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="35" t="n"/>
+      <c r="F100" s="35" t="n"/>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="A101" s="35" t="n"/>
+      <c r="B101" s="35" t="n"/>
+      <c r="C101" s="35" t="n"/>
+      <c r="D101" s="35" t="n"/>
+      <c r="E101" s="35" t="n"/>
+      <c r="F101" s="35" t="n"/>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="35" t="n"/>
+      <c r="B102" s="35" t="n"/>
+      <c r="C102" s="35" t="n"/>
+      <c r="D102" s="35" t="n"/>
+      <c r="E102" s="35" t="n"/>
+      <c r="F102" s="35" t="n"/>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="A103" s="35" t="n"/>
+      <c r="B103" s="35" t="n"/>
+      <c r="C103" s="35" t="n"/>
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="35" t="n"/>
+      <c r="F103" s="35" t="n"/>
+    </row>
+    <row r="104" ht="26" customHeight="1">
+      <c r="A104" s="35" t="n"/>
+      <c r="B104" s="35" t="n"/>
+      <c r="C104" s="35" t="n"/>
+      <c r="D104" s="35" t="n"/>
+      <c r="E104" s="35" t="n"/>
+      <c r="F104" s="35" t="n"/>
+    </row>
+    <row r="105" ht="26" customHeight="1">
+      <c r="A105" s="35" t="n"/>
+      <c r="B105" s="35" t="n"/>
+      <c r="C105" s="35" t="n"/>
+      <c r="D105" s="35" t="n"/>
+      <c r="E105" s="35" t="n"/>
+      <c r="F105" s="35" t="n"/>
+    </row>
+    <row r="106" ht="26" customHeight="1">
+      <c r="A106" s="35" t="n"/>
+      <c r="B106" s="35" t="n"/>
+      <c r="C106" s="35" t="n"/>
+      <c r="D106" s="35" t="n"/>
+      <c r="E106" s="35" t="n"/>
+      <c r="F106" s="35" t="n"/>
+    </row>
+    <row r="107" ht="26" customHeight="1">
+      <c r="A107" s="35" t="n"/>
+      <c r="B107" s="35" t="n"/>
+      <c r="C107" s="35" t="n"/>
+      <c r="D107" s="35" t="n"/>
+      <c r="E107" s="35" t="n"/>
+      <c r="F107" s="35" t="n"/>
+    </row>
+    <row r="108" ht="26" customHeight="1">
+      <c r="A108" s="13" t="inlineStr">
         <is>
           <t>A model version bump, a framework upgrade, a new tool, or a change of host all produce a row. Answer the last column every time, because an auditor will ask which changes went live without a fresh sign-off.</t>
         </is>
@@ -3808,151 +3853,166 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="131">
+  <mergeCells count="143">
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C61:F61"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C91:F91"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C75:F75"/>
     <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C73:F73"/>
     <mergeCell ref="C59:F59"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C64:F64"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C83:F83"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C82:F82"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D34:D45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="D36:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Wider,Narrower,The same"</formula1>
     </dataValidation>
-    <dataValidation sqref="E34:E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E36:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Gateway,Policy engine,Scoped credential,Tool wrapper,Nowhere"</formula1>
     </dataValidation>
-    <dataValidation sqref="C16 C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C18 C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Level 1 — Hand-scoped,Level 2 — Classification ceiling,Level 3 — Policy as code"</formula1>
     </dataValidation>
-    <dataValidation sqref="F90:F99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F98:F107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"A pipeline check,A registry gate,A named person,Nothing"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
@@ -3974,7 +4034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4276,7 +4336,7 @@
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>What you deliberately do NOT record, and why</t>
+          <t>How you would know these records had stopped being collected, and how long after</t>
         </is>
       </c>
       <c r="B27" s="15" t="n"/>
@@ -4285,17 +4345,17 @@
       <c r="E27" s="36" t="n"/>
       <c r="F27" s="34" t="n"/>
     </row>
-    <row r="28" ht="13" customHeight="1">
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Usually personal data you have no basis to retain. Say what you lose by not recording it.</t>
+          <t>The alerts in section C stop firing because nothing arrives to fire them, and stage 5 reads green against records nobody is writing. Section B asks the same question of the evals.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Who can read these records, and who can change them</t>
+          <t>What you deliberately do NOT record, and why</t>
         </is>
       </c>
       <c r="B29" s="15" t="n"/>
@@ -4307,60 +4367,60 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
+          <t>Usually personal data you have no basis to retain. Say what you lose by not recording it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Who can read these records, and who can change them</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="34" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
           <t>If the team that operates the agent can edit its own logs, say so here. Stage 5 needs records an auditor will accept.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="32" t="n"/>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="32" t="n"/>
+      <c r="B33" s="32" t="n"/>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="32" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>B.  The evals, and what runs them</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Which evals run against the live agent</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="34" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="34" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>What starts them</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="35" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="34" t="n"/>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>A schedule, a deployment, live traffic, or a person. An eval a person has to remember to run is not assurance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="56" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>How often, or what share of live traffic if they run continuously</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
@@ -4369,22 +4429,17 @@
       <c r="E36" s="36" t="n"/>
       <c r="F36" s="34" t="n"/>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Where the results go</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="35" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="34" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>A schedule, a deployment, live traffic, or a person. An eval a person has to remember to run is not assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Who is told when one fails</t>
+          <t>How often, or what share of live traffic if they run continuously</t>
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
@@ -4396,7 +4451,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Who owns extending the eval set as the agent changes</t>
+          <t>Where the results go</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
@@ -4405,10 +4460,10 @@
       <c r="E39" s="36" t="n"/>
       <c r="F39" s="34" t="n"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>How you would know they had stopped running, and how long after the run that did not happen</t>
+          <t>Who is told when one fails</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
@@ -4417,17 +4472,22 @@
       <c r="E40" s="36" t="n"/>
       <c r="F40" s="34" t="n"/>
     </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>A dead scheduler and a continuous job that quietly stopped look the same from outside: everything is green because nothing is running.</t>
-        </is>
-      </c>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Who owns extending the eval set as the agent changes</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="35" t="n"/>
+      <c r="D41" s="36" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="34" t="n"/>
     </row>
     <row r="42" ht="56" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Which baseline the results are compared against</t>
+          <t>How you would know they had stopped running, and how long after the run that did not happen</t>
         </is>
       </c>
       <c r="B42" s="15" t="n"/>
@@ -4439,243 +4499,237 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
+          <t>A dead scheduler and a continuous job that quietly stopped look the same from outside: everything is green because nothing is running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="56" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Which baseline the results are compared against</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="35" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="36" t="n"/>
+      <c r="F44" s="34" t="n"/>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
           <t>Normally the eval results recorded at sign-off. Name the version.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="32" t="n"/>
-      <c r="B44" s="32" t="n"/>
-      <c r="C44" s="32" t="n"/>
-      <c r="D44" s="32" t="n"/>
-      <c r="E44" s="32" t="n"/>
-      <c r="F44" s="32" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="32" t="n"/>
+      <c r="B46" s="32" t="n"/>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="32" t="n"/>
+      <c r="F46" s="32" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>C.  What counts as normal, and what starts an alert</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="14" t="inlineStr">
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>What normal looks like</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>What starts an alert</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Who receives it</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Implemented today</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="n"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>A call to a tool outside the declared set</t>
-        </is>
-      </c>
-      <c r="B47" s="35" t="n"/>
-      <c r="C47" s="35" t="n"/>
-      <c r="D47" s="35" t="n"/>
-      <c r="E47" s="35" t="n"/>
-      <c r="F47" s="34" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>Volume of runs</t>
-        </is>
-      </c>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="34" t="n"/>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>What happens if it is not acknowledged, and within what time</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Where it is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>Escalation rate to a person</t>
+          <t>A call to a tool outside the declared set</t>
         </is>
       </c>
       <c r="B49" s="35" t="n"/>
       <c r="C49" s="35" t="n"/>
       <c r="D49" s="35" t="n"/>
       <c r="E49" s="35" t="n"/>
-      <c r="F49" s="34" t="n"/>
+      <c r="F49" s="35" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>Eval failure</t>
+          <t>Volume of runs</t>
         </is>
       </c>
       <c r="B50" s="35" t="n"/>
       <c r="C50" s="35" t="n"/>
       <c r="D50" s="35" t="n"/>
       <c r="E50" s="35" t="n"/>
-      <c r="F50" s="34" t="n"/>
+      <c r="F50" s="35" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>Cost per run or per day</t>
+          <t>Escalation rate to a person</t>
         </is>
       </c>
       <c r="B51" s="35" t="n"/>
       <c r="C51" s="35" t="n"/>
       <c r="D51" s="35" t="n"/>
       <c r="E51" s="35" t="n"/>
-      <c r="F51" s="34" t="n"/>
+      <c r="F51" s="35" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>Error or retry rate</t>
+          <t>Eval failure</t>
         </is>
       </c>
       <c r="B52" s="35" t="n"/>
       <c r="C52" s="35" t="n"/>
       <c r="D52" s="35" t="n"/>
       <c r="E52" s="35" t="n"/>
-      <c r="F52" s="34" t="n"/>
+      <c r="F52" s="35" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>Drift from the design document</t>
+          <t>Cost per run or per day</t>
         </is>
       </c>
       <c r="B53" s="35" t="n"/>
       <c r="C53" s="35" t="n"/>
       <c r="D53" s="35" t="n"/>
       <c r="E53" s="35" t="n"/>
-      <c r="F53" s="34" t="n"/>
+      <c r="F53" s="35" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="37" t="n"/>
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Error or retry rate</t>
+        </is>
+      </c>
       <c r="B54" s="35" t="n"/>
       <c r="C54" s="35" t="n"/>
       <c r="D54" s="35" t="n"/>
       <c r="E54" s="35" t="n"/>
-      <c r="F54" s="34" t="n"/>
-    </row>
-    <row r="55" ht="39" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>Answer the last column for what is implemented today, not what is planned. A row with nothing behind it is a gap the sign-off has to carry. The first row needs the section 3 grant list in a form the monitor can read. It is the only machine-checkable claim in the framework, and naming where the monitor gets it is the difference between an alert you can build and one you intend to.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="32" t="n"/>
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="32" t="n"/>
-      <c r="D56" s="32" t="n"/>
-      <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32" t="n"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="F54" s="35" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Drift from the design document</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="n"/>
+      <c r="C55" s="35" t="n"/>
+      <c r="D55" s="35" t="n"/>
+      <c r="E55" s="35" t="n"/>
+      <c r="F55" s="35" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="37" t="n"/>
+      <c r="B56" s="35" t="n"/>
+      <c r="C56" s="35" t="n"/>
+      <c r="D56" s="35" t="n"/>
+      <c r="E56" s="35" t="n"/>
+      <c r="F56" s="35" t="n"/>
+    </row>
+    <row r="57" ht="66" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>"Where it is implemented" takes the name of the alert, the rule, the monitor or the dashboard: something somebody else could open. Leave it blank where nothing is built, and the sign-off carries the gap. "What happens if it is not acknowledged" is the question section 5 of the Agent Design sheet asks of the agent, asked here of your own alerting: name what happens when the triage time in section D runs out. The first row needs the section 3 grant list in a form the monitor can read, and naming where the monitor gets it is the difference between an alert you can build and one you intend to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="56" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>How long a problem can run before any of the signals above fires</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="35" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="36" t="n"/>
+      <c r="F58" s="34" t="n"/>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>Measured from the moment an action takes effect, not from when somebody looks. Where detection is slower than the undo window in question 5, that window is spent before anybody knows, and it is remaining risk for section C of the Platform &amp; Sign-off sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="32" t="n"/>
+      <c r="B60" s="32" t="n"/>
+      <c r="C60" s="32" t="n"/>
+      <c r="D60" s="32" t="n"/>
+      <c r="E60" s="32" t="n"/>
+      <c r="F60" s="32" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>D.  What an alert starts</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>What happens</t>
         </is>
       </c>
-      <c r="C58" s="15" t="n"/>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>Who does it</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E62" s="14" t="inlineStr">
         <is>
           <t>Within what time</t>
         </is>
       </c>
-      <c r="F58" s="15" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>Triage: is this real</t>
-        </is>
-      </c>
-      <c r="B59" s="35" t="n"/>
-      <c r="C59" s="34" t="n"/>
-      <c r="D59" s="35" t="n"/>
-      <c r="E59" s="35" t="n"/>
-      <c r="F59" s="34" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Contain: stop or narrow the agent</t>
-        </is>
-      </c>
-      <c r="B60" s="35" t="n"/>
-      <c r="C60" s="34" t="n"/>
-      <c r="D60" s="35" t="n"/>
-      <c r="E60" s="35" t="n"/>
-      <c r="F60" s="34" t="n"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>Review the run records</t>
-        </is>
-      </c>
-      <c r="B61" s="35" t="n"/>
-      <c r="C61" s="34" t="n"/>
-      <c r="D61" s="35" t="n"/>
-      <c r="E61" s="35" t="n"/>
-      <c r="F61" s="34" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>Fix</t>
-        </is>
-      </c>
-      <c r="B62" s="35" t="n"/>
-      <c r="C62" s="34" t="n"/>
-      <c r="D62" s="35" t="n"/>
-      <c r="E62" s="35" t="n"/>
-      <c r="F62" s="34" t="n"/>
+      <c r="F62" s="15" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>Tell the people affected</t>
+          <t>Triage: is this real</t>
         </is>
       </c>
       <c r="B63" s="35" t="n"/>
@@ -4687,7 +4741,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="25" t="inlineStr">
         <is>
-          <t>Decide whether anybody outside has to be told, and start that clock</t>
+          <t>Contain: stop or narrow the agent</t>
         </is>
       </c>
       <c r="B64" s="35" t="n"/>
@@ -4699,7 +4753,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="25" t="inlineStr">
         <is>
-          <t>Review after the incident</t>
+          <t>Review the run records</t>
         </is>
       </c>
       <c r="B65" s="35" t="n"/>
@@ -4711,7 +4765,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="25" t="inlineStr">
         <is>
-          <t>Decide whether the agent resumes, and whether the sign-off still holds</t>
+          <t>Fix</t>
         </is>
       </c>
       <c r="B66" s="35" t="n"/>
@@ -4720,178 +4774,162 @@
       <c r="E66" s="35" t="n"/>
       <c r="F66" s="34" t="n"/>
     </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Tell the people affected</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="n"/>
+      <c r="C67" s="34" t="n"/>
+      <c r="D67" s="35" t="n"/>
+      <c r="E67" s="35" t="n"/>
+      <c r="F67" s="34" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>Decide whether anybody outside has to be told, and start that clock</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="n"/>
+      <c r="C68" s="34" t="n"/>
+      <c r="D68" s="35" t="n"/>
+      <c r="E68" s="35" t="n"/>
+      <c r="F68" s="34" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Review after the incident</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="n"/>
+      <c r="C69" s="34" t="n"/>
+      <c r="D69" s="35" t="n"/>
+      <c r="E69" s="35" t="n"/>
+      <c r="F69" s="34" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>Decide whether the agent resumes, and whether the sign-off still holds</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="n"/>
+      <c r="C70" s="34" t="n"/>
+      <c r="D70" s="35" t="n"/>
+      <c r="E70" s="35" t="n"/>
+      <c r="F70" s="34" t="n"/>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>For an agent inside a regulated process, notifying a regulator or a data-protection authority runs on a clock that starts well before the fix is finished. Stage 2 classifies agents on whether a mistake is reportable, so somebody has to decide here whether this one is.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="26" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>The stage 3 sign-off is void once live behavior stops matching what it was granted against, and an incident is that moment. Name who re-confirms it, or re-issues it, before the agent runs again.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="32" t="n"/>
-      <c r="B69" s="32" t="n"/>
-      <c r="C69" s="32" t="n"/>
-      <c r="D69" s="32" t="n"/>
-      <c r="E69" s="32" t="n"/>
-      <c r="F69" s="32" t="n"/>
-    </row>
-    <row r="70" ht="56" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="32" t="n"/>
+      <c r="B73" s="32" t="n"/>
+      <c r="C73" s="32" t="n"/>
+      <c r="D73" s="32" t="n"/>
+      <c r="E73" s="32" t="n"/>
+      <c r="F73" s="32" t="n"/>
+    </row>
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>How the agent is stopped, and by whom</t>
         </is>
       </c>
-      <c r="B70" s="15" t="n"/>
-      <c r="C70" s="35" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
-      <c r="F70" s="34" t="n"/>
-    </row>
-    <row r="71" ht="13" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="35" t="n"/>
+      <c r="D74" s="36" t="n"/>
+      <c r="E74" s="36" t="n"/>
+      <c r="F74" s="34" t="n"/>
+    </row>
+    <row r="75" ht="13" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Point at section 5 of the design document rather than restating it. Say who is on call.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="56" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+    <row r="76" ht="56" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>What you tell a customer, and who decides</t>
         </is>
       </c>
-      <c r="B72" s="15" t="n"/>
-      <c r="C72" s="35" t="n"/>
-      <c r="D72" s="36" t="n"/>
-      <c r="E72" s="36" t="n"/>
-      <c r="F72" s="34" t="n"/>
-    </row>
-    <row r="73" ht="13" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="35" t="n"/>
+      <c r="D76" s="36" t="n"/>
+      <c r="E76" s="36" t="n"/>
+      <c r="F76" s="34" t="n"/>
+    </row>
+    <row r="77" ht="13" customHeight="1">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>For any agent where the person on the other end is not internal staff. Say also how that person challenges the outcome, pointing at section 5 of the design document rather than restating it.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="32" t="n"/>
-      <c r="B74" s="32" t="n"/>
-      <c r="C74" s="32" t="n"/>
-      <c r="D74" s="32" t="n"/>
-      <c r="E74" s="32" t="n"/>
-      <c r="F74" s="32" t="n"/>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>E.  What goes wrong, and what you do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="38" customHeight="1">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>Agents fail in ways ordinary software does not. Write what you would do, or write "not covered" and let the sign-off carry it. Where a row does not apply, write "the agent cannot do this" rather than leaving it blank. Drawn from the OWASP Top 10 for Agentic Applications; the OWASP column names the entry each row comes from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="14" t="inlineStr">
-        <is>
-          <t>What goes wrong</t>
-        </is>
-      </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>OWASP</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>What you do</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="25" t="inlineStr">
-        <is>
-          <t>The agent calls a tool outside its declared set</t>
-        </is>
-      </c>
-      <c r="B78" s="25" t="inlineStr">
-        <is>
-          <t>ASI02, ASI03</t>
-        </is>
-      </c>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="32" t="n"/>
+      <c r="B78" s="32" t="n"/>
       <c r="C78" s="32" t="n"/>
       <c r="D78" s="32" t="n"/>
       <c r="E78" s="32" t="n"/>
       <c r="F78" s="32" t="n"/>
     </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="25" t="inlineStr">
-        <is>
-          <t>A chain of tool calls each succeeds but the outcome is wrong</t>
-        </is>
-      </c>
-      <c r="B79" s="25" t="inlineStr">
-        <is>
-          <t>ASI08</t>
-        </is>
-      </c>
-      <c r="C79" s="32" t="n"/>
-      <c r="D79" s="32" t="n"/>
-      <c r="E79" s="32" t="n"/>
-      <c r="F79" s="32" t="n"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>Prompt injection through content the agent reads</t>
-        </is>
-      </c>
-      <c r="B80" s="25" t="inlineStr">
-        <is>
-          <t>ASI01</t>
-        </is>
-      </c>
-      <c r="C80" s="32" t="n"/>
-      <c r="D80" s="32" t="n"/>
-      <c r="E80" s="32" t="n"/>
-      <c r="F80" s="32" t="n"/>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>E.  What goes wrong, and what you do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="38" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Agents fail in ways ordinary software does not. Write what you would do, or write "not covered" and let the sign-off carry it. Where a row does not apply, write "the agent cannot do this" rather than leaving it blank. Drawn from the OWASP Top 10 for Agentic Applications; the OWASP column names the entry each row comes from.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="25" t="inlineStr">
-        <is>
-          <t>Scope creep: used for work it was not designed for</t>
-        </is>
-      </c>
-      <c r="B81" s="25" t="inlineStr">
-        <is>
-          <t>ASI09</t>
-        </is>
-      </c>
-      <c r="C81" s="32" t="n"/>
-      <c r="D81" s="32" t="n"/>
-      <c r="E81" s="32" t="n"/>
-      <c r="F81" s="32" t="n"/>
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>What goes wrong</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>OWASP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>What you do</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="25" t="inlineStr">
         <is>
-          <t>The agent loops, or runs away on cost</t>
+          <t>The agent calls a tool outside its declared set</t>
         </is>
       </c>
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>ASI08</t>
+          <t>ASI02, ASI03</t>
         </is>
       </c>
       <c r="C82" s="32" t="n"/>
@@ -4902,12 +4940,12 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="25" t="inlineStr">
         <is>
-          <t>A model or framework update changes behavior with no code change</t>
+          <t>A chain of tool calls each succeeds but the outcome is wrong</t>
         </is>
       </c>
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>ASI04</t>
+          <t>ASI08</t>
         </is>
       </c>
       <c r="C83" s="32" t="n"/>
@@ -4918,12 +4956,12 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="25" t="inlineStr">
         <is>
-          <t>Memory or retrieved context has been poisoned</t>
+          <t>Prompt injection through content the agent reads</t>
         </is>
       </c>
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>ASI06</t>
+          <t>ASI01</t>
         </is>
       </c>
       <c r="C84" s="32" t="n"/>
@@ -4934,7 +4972,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="25" t="inlineStr">
         <is>
-          <t>The agent is confidently wrong and a person acts on it</t>
+          <t>Scope creep: used for work it was not designed for</t>
         </is>
       </c>
       <c r="B85" s="25" t="inlineStr">
@@ -4950,12 +4988,12 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="25" t="inlineStr">
         <is>
-          <t>The agent stops escalating when it should</t>
+          <t>The agent loops, or runs away on cost</t>
         </is>
       </c>
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>ASI09</t>
+          <t>ASI08</t>
         </is>
       </c>
       <c r="C86" s="32" t="n"/>
@@ -4966,12 +5004,12 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="25" t="inlineStr">
         <is>
-          <t>The agent runs code or shell commands it composed itself</t>
+          <t>A model or framework update changes behavior with no code change</t>
         </is>
       </c>
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>ASI05</t>
+          <t>ASI04</t>
         </is>
       </c>
       <c r="C87" s="32" t="n"/>
@@ -4982,12 +5020,12 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="25" t="inlineStr">
         <is>
-          <t>A supervising agent fails, or supervises wrongly</t>
+          <t>Memory or retrieved context has been poisoned</t>
         </is>
       </c>
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>ASI07, ASI10</t>
+          <t>ASI06</t>
         </is>
       </c>
       <c r="C88" s="32" t="n"/>
@@ -4995,80 +5033,112 @@
       <c r="E88" s="32" t="n"/>
       <c r="F88" s="32" t="n"/>
     </row>
-    <row r="89" ht="26" customHeight="1">
-      <c r="A89" s="32" t="n"/>
-      <c r="B89" s="32" t="n"/>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="25" t="inlineStr">
+        <is>
+          <t>The agent is confidently wrong and a person acts on it</t>
+        </is>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>ASI09</t>
+        </is>
+      </c>
       <c r="C89" s="32" t="n"/>
       <c r="D89" s="32" t="n"/>
       <c r="E89" s="32" t="n"/>
       <c r="F89" s="32" t="n"/>
     </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="9" t="inlineStr">
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="25" t="inlineStr">
+        <is>
+          <t>The agent stops escalating when it should</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>ASI09</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="n"/>
+      <c r="D90" s="32" t="n"/>
+      <c r="E90" s="32" t="n"/>
+      <c r="F90" s="32" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="25" t="inlineStr">
+        <is>
+          <t>The agent runs code or shell commands it composed itself</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>ASI05</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="n"/>
+      <c r="D91" s="32" t="n"/>
+      <c r="E91" s="32" t="n"/>
+      <c r="F91" s="32" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="25" t="inlineStr">
+        <is>
+          <t>A supervising agent fails, or supervises wrongly</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>ASI07, ASI10</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="n"/>
+      <c r="D92" s="32" t="n"/>
+      <c r="E92" s="32" t="n"/>
+      <c r="F92" s="32" t="n"/>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="32" t="n"/>
+      <c r="B93" s="32" t="n"/>
+      <c r="C93" s="32" t="n"/>
+      <c r="D93" s="32" t="n"/>
+      <c r="E93" s="32" t="n"/>
+      <c r="F93" s="32" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>F.  Revision history</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="14" t="inlineStr">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr">
+      <c r="D95" s="14" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="E91" s="14" t="inlineStr">
+      <c r="E95" s="14" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="F91" s="15" t="n"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="35" t="n"/>
-      <c r="B92" s="35" t="n"/>
-      <c r="C92" s="35" t="n"/>
-      <c r="D92" s="35" t="n"/>
-      <c r="E92" s="35" t="n"/>
-      <c r="F92" s="34" t="n"/>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="35" t="n"/>
-      <c r="B93" s="35" t="n"/>
-      <c r="C93" s="35" t="n"/>
-      <c r="D93" s="35" t="n"/>
-      <c r="E93" s="35" t="n"/>
-      <c r="F93" s="34" t="n"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="35" t="n"/>
-      <c r="B94" s="35" t="n"/>
-      <c r="C94" s="35" t="n"/>
-      <c r="D94" s="35" t="n"/>
-      <c r="E94" s="35" t="n"/>
-      <c r="F94" s="34" t="n"/>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="35" t="n"/>
-      <c r="B95" s="35" t="n"/>
-      <c r="C95" s="35" t="n"/>
-      <c r="D95" s="35" t="n"/>
-      <c r="E95" s="35" t="n"/>
-      <c r="F95" s="34" t="n"/>
+      <c r="F95" s="15" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="35" t="n"/>
@@ -5102,131 +5172,160 @@
       <c r="E99" s="35" t="n"/>
       <c r="F99" s="34" t="n"/>
     </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="35" t="n"/>
+      <c r="B100" s="35" t="n"/>
+      <c r="C100" s="35" t="n"/>
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="35" t="n"/>
+      <c r="F100" s="34" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="35" t="n"/>
+      <c r="B101" s="35" t="n"/>
+      <c r="C101" s="35" t="n"/>
+      <c r="D101" s="35" t="n"/>
+      <c r="E101" s="35" t="n"/>
+      <c r="F101" s="34" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="35" t="n"/>
+      <c r="B102" s="35" t="n"/>
+      <c r="C102" s="35" t="n"/>
+      <c r="D102" s="35" t="n"/>
+      <c r="E102" s="35" t="n"/>
+      <c r="F102" s="34" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="35" t="n"/>
+      <c r="B103" s="35" t="n"/>
+      <c r="C103" s="35" t="n"/>
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="35" t="n"/>
+      <c r="F103" s="34" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="116">
+  <mergeCells count="113">
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="A75:F75"/>
-    <mergeCell ref="C72:F72"/>
     <mergeCell ref="C81:F81"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="A55:F55"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C87:F87"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="B67:C67"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="C89:F89"/>
     <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B69:C69"/>
     <mergeCell ref="E99:F99"/>
-    <mergeCell ref="C79:F79"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="C88:F88"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="E101:F101"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E100:F100"/>
     <mergeCell ref="B63:C63"/>
-    <mergeCell ref="E93:F93"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E102:F102"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="E67:F67"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="B66:C66"/>
-    <mergeCell ref="E48:F48"/>
     <mergeCell ref="C83:F83"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="C92:F92"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="D21:F21"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="C76:F76"/>
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C91:F91"/>
     <mergeCell ref="C82:F82"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="B58:C58"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="E103:F103"/>
     <mergeCell ref="C86:F86"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C58:F58"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="E46:F46"/>
     <mergeCell ref="E95:F95"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="D20:F20"/>
+    <mergeCell ref="C44:F44"/>
     <mergeCell ref="C84:F84"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="E96:F96"/>
-    <mergeCell ref="C70:F70"/>
     <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="E98:F98"/>
+    <mergeCell ref="C38:F38"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C38:F38"/>
     <mergeCell ref="A57:F57"/>
-    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B70:C70"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="E60:F60"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="C85:F85"/>
+    <mergeCell ref="A77:F77"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="B68:C68"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="E97:F97"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C10 C11 C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Level 1 — Tool call log,Level 2 — Run records,Level 3 — Replay and test"</formula1>
     </dataValidation>
-    <dataValidation sqref="B18:B25 E47:E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B18:B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,Partly"</formula1>
     </dataValidation>
   </dataValidations>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -928,7 +928,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
@@ -1851,7 +1851,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="104">
     <mergeCell ref="C68:G68"/>
     <mergeCell ref="A17:G17"/>
@@ -2357,7 +2357,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="32">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A24:B24"/>
@@ -2758,7 +2758,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="5">
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
@@ -3852,7 +3852,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="143">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="C61:F61"/>
@@ -3895,8 +3895,8 @@
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="C27:F27"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="A30:B30"/>
@@ -5205,7 +5205,7 @@
       <c r="F103" s="34" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="113">
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="E62:F62"/>
@@ -6393,7 +6393,7 @@
       <c r="F103" s="34" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="120">
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="E62:F62"/>
@@ -7082,7 +7082,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="8">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>

--- a/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
+++ b/deliverables/agent-governance-assurance-framework/artifacts/agent-governance-forms.xlsx
@@ -748,7 +748,7 @@
       <c r="A8" s="32" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -970,7 +970,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
       <c r="B2" s="32" t="n"/>
@@ -1976,7 +1976,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2012,7 +2012,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
       <c r="B2" s="32" t="n"/>
@@ -2401,7 +2401,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2437,7 +2437,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
       <c r="B2" s="32" t="n"/>
@@ -4019,7 +4019,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4055,7 +4055,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
       <c r="B2" s="32" t="n"/>
@@ -5333,7 +5333,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5369,7 +5369,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
       <c r="B2" s="32" t="n"/>
@@ -6534,7 +6534,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6567,7 +6567,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>September 2026 Draft</t>
+          <t>Unreleased working copy</t>
         </is>
       </c>
       <c r="B2" s="32" t="n"/>
@@ -7097,7 +7097,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, September 2026 Draft&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K595959MACH Alliance — Agent Governance and Assurance Framework, Unreleased working copy&amp;R&amp;8 &amp;K595959&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
